--- a/i18n/de.xlsx
+++ b/i18n/de.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Birds" sheetId="1" r:id="rId1"/>
@@ -6095,9 +6095,6 @@
     <t>2 - 3 Vögel: 3[point]; 4+ Vögel: 7[point]</t>
   </si>
   <si>
-    <t>Durch sprachliche Unterschiede bei den Trivialnamen ändert sich die Prozentzahl und damit auch die Punktewertung einzelner Bonuskarten deutlich, sodass wir empfehlen, bei bestimmten  ogelkartenKombinationen aus Grundspiel und/oder Erweiterungen, einzelne Bonuskarten zu entfernen. Ansonsten bleibt die unktewertung der Bonuskarten gleich. Eine Übersicht findet ihr in der Tabelle.&lt;br&gt;&lt;table&gt;&lt;th&gt;Vogelkarten-Kombination&lt;/th&gt;&lt;th&gt;Zu entfernende Bonuskarten&lt;/th&gt;&lt;tr&gt;&lt;td&gt;Grundspiel, Ozeanien&lt;/td&gt;&lt;td&gt;Biologe, Morphologe&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;Grundspiel, Europa, Ozeanien&lt;/td&gt;&lt;td&gt;Geograf&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;Europa, Ozeanien&lt;/td&gt;&lt;td&gt;Biologe, Geograf&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;Grundspiel, Asien, Europa&lt;/td&gt;&lt;td&gt;Geograf, Morphologe&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;Grundspiel, Asien, Ozeanien&lt;/td&gt;&lt;td&gt;Biologe, Geograf&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;Grundspiel, Asien, Europa, Ozeanien&lt;/td&gt;&lt;td&gt;Biologe, Geograf&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;Asien, Europa&lt;/td&gt;&lt;td&gt;Biologe, Geograf, Morphologe&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;Asien, Ozeanien&lt;/td&gt;&lt;td&gt;Biologe, Fotograf, Geograf, Morphologe&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;Asien, Europa, Ozeanien&lt;/td&gt;&lt;td&gt;Biologe, Geograf&lt;/td&gt;&lt;/tr&gt;&lt;/table&gt;</t>
-  </si>
-  <si>
     <t>Backyard Birder</t>
   </si>
   <si>
@@ -6140,9 +6137,6 @@
     <t>Bird Counter</t>
   </si>
   <si>
-    <t xml:space="preserve">Vogelzähler </t>
-  </si>
-  <si>
     <t>Vögel mit [flocking] Fähigkeit</t>
   </si>
   <si>
@@ -6251,18 +6245,12 @@
     <t>Falconer</t>
   </si>
   <si>
-    <t xml:space="preserve">Falkner </t>
-  </si>
-  <si>
     <t>Vögel mit [predator] Fähigkeit</t>
   </si>
   <si>
     <t>Fishery Manager</t>
   </si>
   <si>
-    <t xml:space="preserve">Fischer </t>
-  </si>
-  <si>
     <t>[fish] fressende Vögel</t>
   </si>
   <si>
@@ -6272,9 +6260,6 @@
     <t>Food Web Expert</t>
   </si>
   <si>
-    <t xml:space="preserve">Schneckenfreund </t>
-  </si>
-  <si>
     <t>Nur [invertebrate] fressende Vögel</t>
   </si>
   <si>
@@ -6284,9 +6269,6 @@
     <t>Forester</t>
   </si>
   <si>
-    <t xml:space="preserve">Förster </t>
-  </si>
-  <si>
     <t>Vögel, die nur im [forest] leben können</t>
   </si>
   <si>
@@ -6305,9 +6287,6 @@
     <t>Large Bird Specialist</t>
   </si>
   <si>
-    <t xml:space="preserve">Grossvogelkundler </t>
-  </si>
-  <si>
     <t>Vögel mit einer Spannweite &gt; 65 cm</t>
   </si>
   <si>
@@ -6329,9 +6308,6 @@
     <t>Omnivore Specialist</t>
   </si>
   <si>
-    <t xml:space="preserve">Gourmand </t>
-  </si>
-  <si>
     <t>[wild] fressende Vögel</t>
   </si>
   <si>
@@ -6341,9 +6317,6 @@
     <t>Oologist</t>
   </si>
   <si>
-    <t xml:space="preserve">Oologe </t>
-  </si>
-  <si>
     <t>Vögel mit min. 1 Ei auf ihrer Karte</t>
   </si>
   <si>
@@ -6353,15 +6326,9 @@
     <t>Passerine Specialist</t>
   </si>
   <si>
-    <t xml:space="preserve">Sperlingskundler </t>
-  </si>
-  <si>
     <t>Vögel mit einer Spannweite ≤ 30 cm</t>
   </si>
   <si>
-    <t xml:space="preserve">Fotograf </t>
-  </si>
-  <si>
     <t>Vögel mit Farben / Mustern im Namen</t>
   </si>
   <si>
@@ -6371,9 +6338,6 @@
     <t>Platform Builder</t>
   </si>
   <si>
-    <t xml:space="preserve">Plattformbauer </t>
-  </si>
-  <si>
     <t>Vögel mit [platform] Nest</t>
   </si>
   <si>
@@ -6402,9 +6366,6 @@
   </si>
   <si>
     <t>Visionary Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vogelbeobachter </t>
   </si>
   <si>
     <t>Vogelkarten auf der Hand am Spielende</t>
@@ -6766,57 +6727,6 @@
     <t>Explanatory Text</t>
   </si>
   <si>
-    <t>Bird in Forest</t>
-  </si>
-  <si>
-    <t>Bird in Grassland</t>
-  </si>
-  <si>
-    <t>Bird in Wetland</t>
-  </si>
-  <si>
-    <t>Egg in Forest</t>
-  </si>
-  <si>
-    <t>Egg in Grassland</t>
-  </si>
-  <si>
-    <t>Egg in Wetland</t>
-  </si>
-  <si>
-    <t>Cavity Nest Bird with Egg</t>
-  </si>
-  <si>
-    <t>Bowl Nest Bird with Egg</t>
-  </si>
-  <si>
-    <t>Ground Nest Bird with Egg</t>
-  </si>
-  <si>
-    <t>Platform Nest Bird with Egg</t>
-  </si>
-  <si>
-    <t>Egg in Cavity Nest</t>
-  </si>
-  <si>
-    <t>Egg in Bowl Nest</t>
-  </si>
-  <si>
-    <t>Egg in Ground Nest</t>
-  </si>
-  <si>
-    <t>Egg in Platform Nest</t>
-  </si>
-  <si>
-    <t>Sets of Eggs in 3 Habitats</t>
-  </si>
-  <si>
-    <t>Total Bird</t>
-  </si>
-  <si>
-    <t>Food in Supply</t>
-  </si>
-  <si>
     <t>Futter im eigenen Vorrat</t>
   </si>
   <si>
@@ -6835,9 +6745,6 @@
     <t>Die Anzahl der Vogelkarten auf deiner Hand.</t>
   </si>
   <si>
-    <t>Birds Worth over 4 Points</t>
-  </si>
-  <si>
     <t>Vögel mit Wert größer 4SP</t>
   </si>
   <si>
@@ -6847,18 +6754,12 @@
     <t>Die Anzahl deiner gespielten Vögel mit einem Wert größer 4 Siegpunkten.</t>
   </si>
   <si>
-    <t>Birds with No Eggs</t>
-  </si>
-  <si>
     <t>Vögel ohne Eier</t>
   </si>
   <si>
     <t>Die Anzahl deiner gespielten Vögel, auf denen keine Eier liegen.</t>
   </si>
   <si>
-    <t>Birds in 1 Row</t>
-  </si>
-  <si>
     <t>Vögel in einer Reihe</t>
   </si>
   <si>
@@ -6868,18 +6769,12 @@
     <t>Die Anzahl der gespielten Vögel in deinem Lebensraum mit den meisten Vögeln.</t>
   </si>
   <si>
-    <t>Filled Columns</t>
-  </si>
-  <si>
     <t>komplett gefüllte Spalten</t>
   </si>
   <si>
     <t>Die Anzahl der Spalten auf deinem Tableau, in denen alle 3 Kartenplätze mit Vögeln belegt sind.</t>
   </si>
   <si>
-    <t>Brown Powers</t>
-  </si>
-  <si>
     <t>Braune Fähigkeiten</t>
   </si>
   <si>
@@ -6889,18 +6784,12 @@
     <t>Die Anzahl deiner gespielten Vögel mit einer braunen Fähigkeit („Bei Aktivierung“).</t>
   </si>
   <si>
-    <t>White &amp; No Powers</t>
-  </si>
-  <si>
     <t>weiße &amp; keine Fähigkeiten</t>
   </si>
   <si>
     <t>Die Anzahl deiner gespielten Vögel mit einer weißen („Beim Ausspielen“) oder ohne Fähigkeit.</t>
   </si>
   <si>
-    <t>Birds with Tucked Cards</t>
-  </si>
-  <si>
     <t>Vögel mit Karten darunter</t>
   </si>
   <si>
@@ -6910,18 +6799,12 @@
     <t>Die Anzahl deiner Vögel unter denen mindestens 1 Karte liegt.</t>
   </si>
   <si>
-    <t>Food Cost of Played Birds</t>
-  </si>
-  <si>
     <t>Futterkosten gespielter Vögel</t>
   </si>
   <si>
     <t>Zähle die Futterkosten deiner Vögel. Kannst du zwischen Futterarten wählen, zähle die Kosten nur einmal.</t>
   </si>
   <si>
-    <t>Invertebrate in Food Cost of Your Birds</t>
-  </si>
-  <si>
     <t>Wirbellose in den Futterkosten eurer Vögel</t>
   </si>
   <si>
@@ -6929,9 +6812,6 @@
   </si>
   <si>
     <t>Zählt die Anzahl der Futtersymbole auf euren gespielten Vögeln, die dem Futtersymbol auf dem Rundenziel entsprechen. Zähle zum Beispiel für das Rundenziel „[fruit]+[seed] in den Futterkosten deiner Vögel“ die Anzahl aller [fruit] plus der Anzahl aller [seed] in den Futterkosten der Vögel auf eurem Spielertableau. Hat ein Vogel „[fruit]/[seed]“ Futterkosten (du hast also 1 [fruit] ODER 1 [seed] bezahlt, um den Vogel zu spielen), zählt dies nur als 1 für das Rundenziel (nicht als 2). [wild] und [nectar] zählen nicht.</t>
-  </si>
-  <si>
-    <t>Fruit + Seed in Food Cost of Your Birds</t>
   </si>
   <si>
     <t>Früchte + Samen in den Futterkosten eurer Vögel</t>
@@ -6957,9 +6837,6 @@
     </r>
   </si>
   <si>
-    <t>Rodent + Fish in Food Cost of Your Birds</t>
-  </si>
-  <si>
     <t>Nager + Fische in den Futterkosten eurer Vögel</t>
   </si>
   <si>
@@ -6983,18 +6860,12 @@
     </r>
   </si>
   <si>
-    <t>No Goal</t>
-  </si>
-  <si>
     <t>Kein Ziel</t>
   </si>
   <si>
     <t>Am Ende dieser Runde wird kein Rundenziel gewertet. Ihr behaltet euren Aktionswürfel. In den folgenden Runden könnt ihr also eine Aktion mehr machen als üblich.</t>
   </si>
   <si>
-    <t>Beak Pointing Left</t>
-  </si>
-  <si>
     <t>Schnabel zeigt nach links</t>
   </si>
   <si>
@@ -7004,18 +6875,12 @@
     <t>Für diese Rundenziele zählen eure gespielten Vögel, deren Schnabel in die angegebene Richtung zeigt. Vögel, deren Schnabel nach vorn oder senkrecht nach oben zeigt, zählen für keines der beiden Rundenziele.&lt;br&gt;Diese Rundenziele sollen euch ermutigen, euch die Illustrationen noch genauer anzusehen. Falls ihr euch häufig nicht einigen könnt, in welche Richtung der Schnabel zeigt, entfernt dieses Zielplättchen aus dem Spiel. Auch wenn wir finden, dass man die Schnabelrichtung meist gut zuordnen kann, möchten wir folgendes klarstellen:&lt;br&gt;&lt;ul&gt;&lt;li&gt;Obwohl der Schiefschnabel (Ozeanienerweiterung) nach vorn blickt, zeigt sein Schnabel auf die linke Seite der Karte.&lt;/li&gt;&lt;li&gt;Der Eistaucher (Grundspiel) und der Zwergtaucher (Asienerweiterung) zeigen je 1 Vogel, der nach links und 1 Vogel, der nach rechts blickt. Sie zählt daher für beide Ziele.&lt;/li&gt;&lt;li&gt;Der Haubentaucher (Europaerweiterung) zeigt 2 Vögel, die in die gleiche Richtung blicken. Er zählt nur für das Ziel „nach links zeigend“ und auch nur 1x.&lt;/li&gt;&lt;/ul&gt;&lt;br&gt;Die Schnäbel der folgenden Vögel zeigen weder nach rechts noch nach links.&lt;br&gt;&lt;b&gt;Grundspiel&lt;/b&gt;&lt;ul&gt;&lt;li&gt;Fleckenkauz&lt;/li&gt;&lt;li&gt;Kalifornischer Kondor&lt;/li&gt;&lt;li&gt;Kaninchenkauz&lt;/li&gt;&lt;li&gt;Ohrenlerche&lt;/li&gt;&lt;li&gt;Ostkreischeule&lt;/li&gt;&lt;li&gt;Schleiereule&lt;/li&gt;&lt;li&gt;Streifenkauz&lt;/li&gt;&lt;li&gt;Virginiauhu&lt;/li&gt;&lt;/ul&gt;&lt;b&gt;Europa-Erweiterung&lt;/b&gt;&lt;ul&gt;&lt;li&gt;Gartenbaumläufer&lt;/li&gt;&lt;li&gt;Schneeeule&lt;/li&gt;&lt;li&gt;Steinkauz&lt;/li&gt;&lt;/ul&gt;&lt;b&gt;Ozeanien-Erweiterung&lt;/b&gt;&lt;ul&gt;&lt;li&gt;Baumschwalm&lt;/li&gt;&lt;li&gt;Kakapo&lt;/li&gt;&lt;li&gt;Rostkauz&lt;/li&gt;&lt;/ul&gt;&lt;b&gt;Asien-Erweiterung&lt;/b&gt;&lt;ul&gt;&lt;li&gt;Bartmeise&lt;/li&gt;&lt;li&gt;Blewittkauz&lt;/li&gt;&lt;li&gt;Ceylonschwalm&lt;/li&gt;&lt;li&gt;Löffelstrandläufer&lt;/li&gt;&lt;li&gt;Maskeneule&lt;/li&gt;&lt;li&gt;Uhu&lt;/li&gt;&lt;/ul&gt;</t>
   </si>
   <si>
-    <t>Beak Pointing Right</t>
-  </si>
-  <si>
     <t>Schnabel zeigt nach rechts</t>
   </si>
   <si>
     <t>[beak-left] Schnabel zeigt nach rechts</t>
   </si>
   <si>
-    <t>Cubes on "Play a Bird"</t>
-  </si>
-  <si>
     <t>Aktionswürfel auf „Vogel spielen“</t>
   </si>
   <si>
@@ -7023,9 +6888,6 @@
   </si>
   <si>
     <t>Zählt die Anzahl der Aktionswürfel, die ihr in dieser Runde auf „Vogel spielen“ gelegt habt. Beachtet: Für die Wertung dieses Rundenziels ist es wichtig, dass ihr die Aktionswürfel bis nach der Wertung in der gespielten Reihe liegen lasst!</t>
-  </si>
-  <si>
-    <t>Birds Worth Less than or Equal to 3 Points</t>
   </si>
   <si>
     <r>
@@ -7057,18 +6919,12 @@
     </r>
   </si>
   <si>
-    <t>Pairs of Matching Symbols</t>
-  </si>
-  <si>
     <t>auf Paaren mit gleichen Symbolen</t>
   </si>
   <si>
     <t>Zähle, wie viele deiner Duellmarker Teil eines Paares (= 2 Marker deiner Farbe) mit dem gleichen Symbol auf einem Feld sind. Jeder Duellmarker zählt nur einmal. Die Symbole müssen genau übereinstimmen wie z. B. 2 Nager oder 2x 50+ cm Spannweite. Boni auf den Feldern müssen nicht übereinstimmen.</t>
   </si>
   <si>
-    <t>Nest Symbols</t>
-  </si>
-  <si>
     <t>auf Nestsymbolen</t>
   </si>
   <si>
@@ -7078,9 +6934,6 @@
     <t>Zähle alle deine Duellmarker auf Feldern mit einem beliebigen Nestsymbol ([bowl] [cavity] [ground] [platform]). Auch mehrere Symbole der gleichen Art zählen (z. B. zählen bei 2 Markern auf unterschiedlichen [platform]-Feldern beide).</t>
   </si>
   <si>
-    <t>Food Symbols</t>
-  </si>
-  <si>
     <t>auf Futtersymbolen</t>
   </si>
   <si>
@@ -7090,9 +6943,6 @@
     <t>Zähle alle deine Duellmarker auf Feldern mit einem beliebigen Futtersymbol ([fruit] [seed] [invertebrate] [rodent] [fish]). Auch mehrere Symbole der gleichen Art zählen (z. B. zählen bei 2 Markern auf unterschiedlichen [fish]-Feldern beide).</t>
   </si>
   <si>
-    <t>Not on Edge of Map</t>
-  </si>
-  <si>
     <t>nicht am Rand der Karte</t>
   </si>
   <si>
@@ -7102,18 +6952,12 @@
     <t>Jeder Rand der Karte hat 6 Felder: Die Seiten haben je 3 eingerückte Felder, die auch als am Rand der Karte zählen. Es gibt also 20 Randfelder und 16 innere Felder. Für diese Ziele zählst du, wie viele deiner Duellmarker am Rand der Karte auf inneren Feldern bzw. Randfeldern liegen.&lt;i&gt; (Beachte: Die Symbole der Lebensräume zählen nicht als Felder.)&lt;/i&gt;</t>
   </si>
   <si>
-    <t>On Edge of Map</t>
-  </si>
-  <si>
     <t>am Rand der Karte</t>
   </si>
   <si>
     <t>[duet-token] am Rand der Karte</t>
   </si>
   <si>
-    <t>Tokens in Any One Horizontal Row</t>
-  </si>
-  <si>
     <t>in 1 beliebigen horizontalen Reihe</t>
   </si>
   <si>
@@ -7123,18 +6967,12 @@
     <t>Bestimme die horizontale Reihe der Karte, die für dich am besten ist und zähle die Anzahl deiner Duellmarker in dieser Reihe. Die Duellmarker müssen keine zusammenhängende Gruppe bilden.</t>
   </si>
   <si>
-    <t>Horizontal Rows with at Least One of Your Tokens</t>
-  </si>
-  <si>
     <t>Horizontale Reihen mit mind. 1 deiner Duellmarker</t>
   </si>
   <si>
     <t>Zähle, in wie vielen der 6 horizontalen Reihen mindestens 1 deiner Duellmarker liegt.</t>
   </si>
   <si>
-    <t>Fewest Tokens on Bonus Spaces</t>
-  </si>
-  <si>
     <t>Wenigste Duellmarker auf Bonusfeldern</t>
   </si>
   <si>
@@ -7144,9 +6982,6 @@
     <t>Bonusfelder sind Felder, durch die ihr [dice]/[egg]/[card] erhaltet, wenn ihr einen Duellmarker darauf legt. Zähle wie viele deiner Duellmarker auf diesen 9 Feldern liegen. Die Punkte für dieses Rundenziel erhält, wer weniger Duellmarker auf Bonusfeldern hat.</t>
   </si>
   <si>
-    <t>In Forest</t>
-  </si>
-  <si>
     <t>im Wald</t>
   </si>
   <si>
@@ -7156,27 +6991,18 @@
     <t>Zähle die Anzahl deiner Duellmarker im Bereich des entsprechenden Lebensraums auf der Duellkarte. Diese Zahl kann von der Zahl der Vögel auf deinem Tableau abweichen, falls sich Vögel während des Spiels bewegt haben (durch eine Fähigkeit).</t>
   </si>
   <si>
-    <t>In Grassland</t>
-  </si>
-  <si>
     <t>im Grasland</t>
   </si>
   <si>
     <t>[duet-token] im [grassland]</t>
   </si>
   <si>
-    <t>In Wetland</t>
-  </si>
-  <si>
     <t>im Wasser</t>
   </si>
   <si>
     <t>[duet-token] im [wetland]</t>
   </si>
   <si>
-    <t>Total Duet Tokens</t>
-  </si>
-  <si>
     <t>auf der Karte</t>
   </si>
   <si>
@@ -7523,6 +7349,180 @@
   </si>
   <si>
     <t>In den 1980ern gab es nur noch 22 dieser Aasfresser. Nun gibt es wieder über 200 Vögel.</t>
+  </si>
+  <si>
+    <t>Durch sprachliche Unterschiede bei den Trivialnamen ändert sich die Prozentzahl und damit auch die Punktewertung einzelner Bonuskarten deutlich, sodass wir empfehlen, bei bestimmten ogelkartenKombinationen aus Grundspiel und/oder Erweiterungen, einzelne Bonuskarten zu entfernen. Ansonsten bleibt die unktewertung der Bonuskarten gleich. Eine Übersicht findet ihr in der Tabelle.&lt;br&gt;&lt;table&gt;&lt;th&gt;Vogelkarten-Kombination&lt;/th&gt;&lt;th&gt;Zu entfernende Bonuskarten&lt;/th&gt;&lt;tr&gt;&lt;td&gt;Grundspiel, Ozeanien&lt;/td&gt;&lt;td&gt;Biologe, Morphologe&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;Grundspiel, Europa, Ozeanien&lt;/td&gt;&lt;td&gt;Geograf&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;Europa, Ozeanien&lt;/td&gt;&lt;td&gt;Biologe, Geograf&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;Grundspiel, Asien, Europa&lt;/td&gt;&lt;td&gt;Geograf, Morphologe&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;Grundspiel, Asien, Ozeanien&lt;/td&gt;&lt;td&gt;Biologe, Geograf&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;Grundspiel, Asien, Europa, Ozeanien&lt;/td&gt;&lt;td&gt;Biologe, Geograf&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;Asien, Europa&lt;/td&gt;&lt;td&gt;Biologe, Geograf, Morphologe&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;Asien, Ozeanien&lt;/td&gt;&lt;td&gt;Biologe, Fotograf, Geograf, Morphologe&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;Asien, Europa, Ozeanien&lt;/td&gt;&lt;td&gt;Biologe, Geograf&lt;/td&gt;&lt;/tr&gt;&lt;/table&gt;</t>
+  </si>
+  <si>
+    <t>Vogelzähler</t>
+  </si>
+  <si>
+    <t>Falkner</t>
+  </si>
+  <si>
+    <t>Fischer</t>
+  </si>
+  <si>
+    <t>Schneckenfreund</t>
+  </si>
+  <si>
+    <t>Förster</t>
+  </si>
+  <si>
+    <t>Grossvogelkundler</t>
+  </si>
+  <si>
+    <t>Gourmand</t>
+  </si>
+  <si>
+    <t>Oologe</t>
+  </si>
+  <si>
+    <t>Sperlingskundler</t>
+  </si>
+  <si>
+    <t>Fotograf</t>
+  </si>
+  <si>
+    <t>Plattformbauer</t>
+  </si>
+  <si>
+    <t>Vogelbeobachter</t>
+  </si>
+  <si>
+    <t>Birds in Forest</t>
+  </si>
+  <si>
+    <t>Birds in Grassland</t>
+  </si>
+  <si>
+    <t>Birds in Wetland</t>
+  </si>
+  <si>
+    <t>Eggs in Forest</t>
+  </si>
+  <si>
+    <t>Eggs in Grassland</t>
+  </si>
+  <si>
+    <t>Eggs in Wetland</t>
+  </si>
+  <si>
+    <t>Eggs in Cavity Nest</t>
+  </si>
+  <si>
+    <t>Eggs in Bowl Nest</t>
+  </si>
+  <si>
+    <t>Eggs in Ground Nest</t>
+  </si>
+  <si>
+    <t>Eggs in Platform Nest</t>
+  </si>
+  <si>
+    <t>Cavity nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Bowl nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Ground nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Platform nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Sets of eggs in 3 habitats</t>
+  </si>
+  <si>
+    <t>Total birds</t>
+  </si>
+  <si>
+    <t>Food in personal supply</t>
+  </si>
+  <si>
+    <t>Birds worth over 4 points</t>
+  </si>
+  <si>
+    <t>Birds with no eggs</t>
+  </si>
+  <si>
+    <t>Filled columns</t>
+  </si>
+  <si>
+    <t>Brown powers</t>
+  </si>
+  <si>
+    <t>White &amp; no powers</t>
+  </si>
+  <si>
+    <t>Birds with tucked cards</t>
+  </si>
+  <si>
+    <t>Food cost of played birds</t>
+  </si>
+  <si>
+    <t>Invertebrate in food cost of your birds</t>
+  </si>
+  <si>
+    <t>Fruit + Seed in food cost of your birds</t>
+  </si>
+  <si>
+    <t>Rodent + Fish in food cost of your birds</t>
+  </si>
+  <si>
+    <t>No goal</t>
+  </si>
+  <si>
+    <t>Beak pointing left</t>
+  </si>
+  <si>
+    <t>Beak pointing right</t>
+  </si>
+  <si>
+    <t>Cubes on "play a bird"</t>
+  </si>
+  <si>
+    <t>Duet tokens on pairs of matching symbols</t>
+  </si>
+  <si>
+    <t>Duet tokens on nest symbols</t>
+  </si>
+  <si>
+    <t>Duet tokens on food symbols</t>
+  </si>
+  <si>
+    <t>Duet tokens in any one horizontal row</t>
+  </si>
+  <si>
+    <t>Horizontal rows with at least 1 of your duet tokens</t>
+  </si>
+  <si>
+    <t>Fewest duet tokens on bonus spaces</t>
+  </si>
+  <si>
+    <t>Duet tokens not on edge of map</t>
+  </si>
+  <si>
+    <t>Duet tokens on edge of map</t>
+  </si>
+  <si>
+    <t>Total duet tokens</t>
+  </si>
+  <si>
+    <t>Duet tokens in Forest</t>
+  </si>
+  <si>
+    <t>Duet tokens in Grassland</t>
+  </si>
+  <si>
+    <t>Duet tokens in Wetland</t>
+  </si>
+  <si>
+    <t>Birds worth less than or equal to 3 points</t>
+  </si>
+  <si>
+    <t>Birds in one row</t>
   </si>
 </sst>
 </file>
@@ -7533,7 +7533,7 @@
     <numFmt numFmtId="164" formatCode="[$SFr.-807]\ #,##0.00;[Red][$SFr.-807]&quot; -&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;PRAWDA&quot;;&quot;PRAWDA&quot;;&quot;FAŁSZ&quot;"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -7624,6 +7624,12 @@
       <name val="Calibri"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -7648,7 +7654,7 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
@@ -7691,6 +7697,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Excel Built-in Normal" xfId="3"/>
@@ -8993,7 +9000,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="25" t="s">
-        <v>2434</v>
+        <v>2376</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>169</v>
@@ -9738,7 +9745,7 @@
         <v>90</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>2440</v>
+        <v>2382</v>
       </c>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
@@ -11131,7 +11138,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="8" t="s">
-        <v>2435</v>
+        <v>2377</v>
       </c>
       <c r="C106" s="3" t="s">
         <v>493</v>
@@ -12117,7 +12124,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>2343</v>
+        <v>2285</v>
       </c>
       <c r="C139" s="3" t="s">
         <v>645</v>
@@ -13286,7 +13293,7 @@
         <v>827</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>2437</v>
+        <v>2379</v>
       </c>
       <c r="D179" s="6" t="s">
         <v>14</v>
@@ -16989,7 +16996,7 @@
         <v>1380</v>
       </c>
       <c r="F303" s="3" t="s">
-        <v>2439</v>
+        <v>2381</v>
       </c>
       <c r="G303" s="7" t="s">
         <v>1381</v>
@@ -17235,7 +17242,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="6" t="s">
-        <v>2436</v>
+        <v>2378</v>
       </c>
       <c r="C312" s="3" t="s">
         <v>1420</v>
@@ -18636,7 +18643,7 @@
         <v>1651</v>
       </c>
       <c r="G358" s="9" t="s">
-        <v>2374</v>
+        <v>2316</v>
       </c>
       <c r="H358" s="4"/>
       <c r="I358" s="4"/>
@@ -18668,7 +18675,7 @@
         <v>1655</v>
       </c>
       <c r="G359" s="9" t="s">
-        <v>2383</v>
+        <v>2325</v>
       </c>
       <c r="H359" s="4"/>
       <c r="I359" s="4"/>
@@ -18698,7 +18705,7 @@
         <v>1659</v>
       </c>
       <c r="G360" s="9" t="s">
-        <v>2389</v>
+        <v>2331</v>
       </c>
       <c r="H360" s="4"/>
       <c r="I360" s="4"/>
@@ -18728,7 +18735,7 @@
         <v>1663</v>
       </c>
       <c r="G361" s="9" t="s">
-        <v>2348</v>
+        <v>2290</v>
       </c>
       <c r="H361" s="4"/>
       <c r="I361" s="4"/>
@@ -18756,7 +18763,7 @@
         <v>1667</v>
       </c>
       <c r="G362" s="9" t="s">
-        <v>2347</v>
+        <v>2289</v>
       </c>
       <c r="H362" s="4"/>
       <c r="I362" s="4"/>
@@ -18784,7 +18791,7 @@
         <v>1671</v>
       </c>
       <c r="G363" s="9" t="s">
-        <v>2385</v>
+        <v>2327</v>
       </c>
       <c r="H363" s="4"/>
       <c r="I363" s="4"/>
@@ -18814,7 +18821,7 @@
         <v>1675</v>
       </c>
       <c r="G364" s="9" t="s">
-        <v>2413</v>
+        <v>2355</v>
       </c>
       <c r="H364" s="4"/>
       <c r="I364" s="4"/>
@@ -18844,7 +18851,7 @@
         <v>1679</v>
       </c>
       <c r="G365" s="9" t="s">
-        <v>2412</v>
+        <v>2354</v>
       </c>
       <c r="H365" s="4"/>
       <c r="I365" s="4" t="s">
@@ -18856,7 +18863,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="366" spans="1:12" ht="105">
+    <row r="366" spans="1:12" ht="90">
       <c r="A366" s="4">
         <v>366</v>
       </c>
@@ -18876,7 +18883,7 @@
         <v>1683</v>
       </c>
       <c r="G366" s="9" t="s">
-        <v>2353</v>
+        <v>2295</v>
       </c>
       <c r="H366" s="4"/>
       <c r="I366" s="4"/>
@@ -18906,7 +18913,7 @@
         <v>1687</v>
       </c>
       <c r="G367" s="9" t="s">
-        <v>2355</v>
+        <v>2297</v>
       </c>
       <c r="H367" s="4"/>
       <c r="I367" s="4"/>
@@ -18934,7 +18941,7 @@
         <v>1691</v>
       </c>
       <c r="G368" s="9" t="s">
-        <v>2349</v>
+        <v>2291</v>
       </c>
       <c r="H368" s="4"/>
       <c r="I368" s="4"/>
@@ -18962,7 +18969,7 @@
         <v>1695</v>
       </c>
       <c r="G369" s="9" t="s">
-        <v>2357</v>
+        <v>2299</v>
       </c>
       <c r="H369" s="4"/>
       <c r="I369" s="4"/>
@@ -18992,7 +18999,7 @@
         <v>1699</v>
       </c>
       <c r="G370" s="9" t="s">
-        <v>2384</v>
+        <v>2326</v>
       </c>
       <c r="H370" s="4"/>
       <c r="I370" s="4"/>
@@ -19022,7 +19029,7 @@
         <v>1703</v>
       </c>
       <c r="G371" s="9" t="s">
-        <v>2368</v>
+        <v>2310</v>
       </c>
       <c r="H371" s="4"/>
       <c r="I371" s="4"/>
@@ -19050,7 +19057,7 @@
         <v>1707</v>
       </c>
       <c r="G372" s="9" t="s">
-        <v>2379</v>
+        <v>2321</v>
       </c>
       <c r="H372" s="4"/>
       <c r="I372" s="4"/>
@@ -19078,7 +19085,7 @@
         <v>1711</v>
       </c>
       <c r="G373" s="9" t="s">
-        <v>2367</v>
+        <v>2309</v>
       </c>
       <c r="H373" s="4"/>
       <c r="I373" s="4"/>
@@ -19106,7 +19113,7 @@
         <v>1715</v>
       </c>
       <c r="G374" s="9" t="s">
-        <v>2407</v>
+        <v>2349</v>
       </c>
       <c r="H374" s="4"/>
       <c r="I374" s="4"/>
@@ -19114,7 +19121,7 @@
       <c r="K374" s="4"/>
       <c r="L374" s="4"/>
     </row>
-    <row r="375" spans="1:12" ht="75">
+    <row r="375" spans="1:12" ht="60">
       <c r="A375" s="4">
         <v>375</v>
       </c>
@@ -19134,7 +19141,7 @@
         <v>1719</v>
       </c>
       <c r="G375" s="9" t="s">
-        <v>2387</v>
+        <v>2329</v>
       </c>
       <c r="H375" s="4"/>
       <c r="I375" s="4"/>
@@ -19164,7 +19171,7 @@
         <v>722</v>
       </c>
       <c r="G376" s="9" t="s">
-        <v>2388</v>
+        <v>2330</v>
       </c>
       <c r="H376" s="4"/>
       <c r="I376" s="4"/>
@@ -19192,7 +19199,7 @@
         <v>1726</v>
       </c>
       <c r="G377" s="9" t="s">
-        <v>2397</v>
+        <v>2339</v>
       </c>
       <c r="H377" s="4"/>
       <c r="I377" s="4" t="s">
@@ -19222,7 +19229,7 @@
         <v>1730</v>
       </c>
       <c r="G378" s="9" t="s">
-        <v>2377</v>
+        <v>2319</v>
       </c>
       <c r="H378" s="4"/>
       <c r="I378" s="4" t="s">
@@ -19252,7 +19259,7 @@
         <v>1734</v>
       </c>
       <c r="G379" s="10" t="s">
-        <v>2425</v>
+        <v>2367</v>
       </c>
       <c r="H379" s="4"/>
       <c r="I379" s="4"/>
@@ -19282,7 +19289,7 @@
         <v>1738</v>
       </c>
       <c r="G380" s="9" t="s">
-        <v>2430</v>
+        <v>2372</v>
       </c>
       <c r="H380" s="4"/>
       <c r="I380" s="4"/>
@@ -19312,7 +19319,7 @@
         <v>1742</v>
       </c>
       <c r="G381" s="9" t="s">
-        <v>2351</v>
+        <v>2293</v>
       </c>
       <c r="H381" s="4"/>
       <c r="I381" s="4"/>
@@ -19342,7 +19349,7 @@
         <v>1746</v>
       </c>
       <c r="G382" s="9" t="s">
-        <v>2421</v>
+        <v>2363</v>
       </c>
       <c r="H382" s="4"/>
       <c r="I382" s="4"/>
@@ -19372,7 +19379,7 @@
         <v>1750</v>
       </c>
       <c r="G383" s="9" t="s">
-        <v>2428</v>
+        <v>2370</v>
       </c>
       <c r="H383" s="4"/>
       <c r="I383" s="4"/>
@@ -19402,7 +19409,7 @@
         <v>1754</v>
       </c>
       <c r="G384" s="9" t="s">
-        <v>2420</v>
+        <v>2362</v>
       </c>
       <c r="H384" s="4"/>
       <c r="I384" s="4"/>
@@ -19432,7 +19439,7 @@
         <v>1746</v>
       </c>
       <c r="G385" s="9" t="s">
-        <v>2401</v>
+        <v>2343</v>
       </c>
       <c r="H385" s="4"/>
       <c r="I385" s="4"/>
@@ -19442,7 +19449,7 @@
       <c r="K385" s="4"/>
       <c r="L385" s="4"/>
     </row>
-    <row r="386" spans="1:12" ht="75">
+    <row r="386" spans="1:12" ht="60">
       <c r="A386" s="4">
         <v>386</v>
       </c>
@@ -19462,7 +19469,7 @@
         <v>1761</v>
       </c>
       <c r="G386" s="9" t="s">
-        <v>2422</v>
+        <v>2364</v>
       </c>
       <c r="H386" s="4"/>
       <c r="I386" s="4"/>
@@ -19492,7 +19499,7 @@
         <v>1765</v>
       </c>
       <c r="G387" s="9" t="s">
-        <v>2406</v>
+        <v>2348</v>
       </c>
       <c r="H387" s="4"/>
       <c r="I387" s="4"/>
@@ -19522,7 +19529,7 @@
         <v>1769</v>
       </c>
       <c r="G388" s="9" t="s">
-        <v>2354</v>
+        <v>2296</v>
       </c>
       <c r="H388" s="4"/>
       <c r="I388" s="4"/>
@@ -19552,7 +19559,7 @@
         <v>1773</v>
       </c>
       <c r="G389" s="9" t="s">
-        <v>2371</v>
+        <v>2313</v>
       </c>
       <c r="H389" s="4"/>
       <c r="I389" s="4"/>
@@ -19582,7 +19589,7 @@
         <v>1777</v>
       </c>
       <c r="G390" s="9" t="s">
-        <v>2418</v>
+        <v>2360</v>
       </c>
       <c r="H390" s="4"/>
       <c r="I390" s="4"/>
@@ -19610,7 +19617,7 @@
         <v>1780</v>
       </c>
       <c r="G391" s="9" t="s">
-        <v>2372</v>
+        <v>2314</v>
       </c>
       <c r="H391" s="4"/>
       <c r="I391" s="4"/>
@@ -19638,7 +19645,7 @@
         <v>1784</v>
       </c>
       <c r="G392" s="9" t="s">
-        <v>2369</v>
+        <v>2311</v>
       </c>
       <c r="H392" s="4"/>
       <c r="I392" s="4" t="s">
@@ -19670,7 +19677,7 @@
         <v>1788</v>
       </c>
       <c r="G393" s="9" t="s">
-        <v>2386</v>
+        <v>2328</v>
       </c>
       <c r="H393" s="4"/>
       <c r="I393" s="4"/>
@@ -19698,7 +19705,7 @@
         <v>1792</v>
       </c>
       <c r="G394" s="9" t="s">
-        <v>2364</v>
+        <v>2306</v>
       </c>
       <c r="H394" s="4"/>
       <c r="I394" s="4" t="s">
@@ -19728,7 +19735,7 @@
         <v>1796</v>
       </c>
       <c r="G395" s="9" t="s">
-        <v>2382</v>
+        <v>2324</v>
       </c>
       <c r="H395" s="4"/>
       <c r="I395" s="4"/>
@@ -19758,7 +19765,7 @@
         <v>1800</v>
       </c>
       <c r="G396" s="9" t="s">
-        <v>2359</v>
+        <v>2301</v>
       </c>
       <c r="H396" s="4"/>
       <c r="I396" s="4"/>
@@ -19786,7 +19793,7 @@
         <v>1804</v>
       </c>
       <c r="G397" s="9" t="s">
-        <v>2373</v>
+        <v>2315</v>
       </c>
       <c r="H397" s="4"/>
       <c r="I397" s="4"/>
@@ -19814,7 +19821,7 @@
         <v>1808</v>
       </c>
       <c r="G398" s="9" t="s">
-        <v>2415</v>
+        <v>2357</v>
       </c>
       <c r="H398" s="4"/>
       <c r="I398" s="4"/>
@@ -19832,7 +19839,7 @@
         <v>1809</v>
       </c>
       <c r="C399" s="4" t="s">
-        <v>2438</v>
+        <v>2380</v>
       </c>
       <c r="D399" s="6" t="s">
         <v>1649</v>
@@ -19844,7 +19851,7 @@
         <v>1811</v>
       </c>
       <c r="G399" s="9" t="s">
-        <v>2358</v>
+        <v>2300</v>
       </c>
       <c r="H399" s="4"/>
       <c r="I399" s="4"/>
@@ -19874,7 +19881,7 @@
         <v>1815</v>
       </c>
       <c r="G400" s="9" t="s">
-        <v>2378</v>
+        <v>2320</v>
       </c>
       <c r="H400" s="4"/>
       <c r="I400" s="4"/>
@@ -19904,7 +19911,7 @@
         <v>1819</v>
       </c>
       <c r="G401" s="9" t="s">
-        <v>2370</v>
+        <v>2312</v>
       </c>
       <c r="H401" s="4"/>
       <c r="I401" s="4"/>
@@ -19912,7 +19919,7 @@
       <c r="K401" s="4"/>
       <c r="L401" s="4"/>
     </row>
-    <row r="402" spans="1:12" ht="75">
+    <row r="402" spans="1:12" ht="60">
       <c r="A402" s="4">
         <v>402</v>
       </c>
@@ -19932,7 +19939,7 @@
         <v>1823</v>
       </c>
       <c r="G402" s="9" t="s">
-        <v>2380</v>
+        <v>2322</v>
       </c>
       <c r="H402" s="4"/>
       <c r="I402" s="4" t="s">
@@ -19962,7 +19969,7 @@
         <v>1827</v>
       </c>
       <c r="G403" s="9" t="s">
-        <v>2352</v>
+        <v>2294</v>
       </c>
       <c r="H403" s="4"/>
       <c r="I403" s="4"/>
@@ -19992,7 +19999,7 @@
         <v>1831</v>
       </c>
       <c r="G404" s="9" t="s">
-        <v>2381</v>
+        <v>2323</v>
       </c>
       <c r="H404" s="4"/>
       <c r="I404" s="4"/>
@@ -20022,7 +20029,7 @@
         <v>1835</v>
       </c>
       <c r="G405" s="9" t="s">
-        <v>2363</v>
+        <v>2305</v>
       </c>
       <c r="H405" s="4"/>
       <c r="I405" s="4" t="s">
@@ -20052,7 +20059,7 @@
         <v>1839</v>
       </c>
       <c r="G406" s="9" t="s">
-        <v>2414</v>
+        <v>2356</v>
       </c>
       <c r="H406" s="4"/>
       <c r="I406" s="4"/>
@@ -20060,7 +20067,7 @@
       <c r="K406" s="4"/>
       <c r="L406" s="4"/>
     </row>
-    <row r="407" spans="1:12" ht="60">
+    <row r="407" spans="1:12" ht="45">
       <c r="A407" s="4">
         <v>407</v>
       </c>
@@ -20080,7 +20087,7 @@
         <v>1843</v>
       </c>
       <c r="G407" s="9" t="s">
-        <v>2433</v>
+        <v>2375</v>
       </c>
       <c r="H407" s="4"/>
       <c r="I407" s="4"/>
@@ -20108,7 +20115,7 @@
         <v>1847</v>
       </c>
       <c r="G408" s="9" t="s">
-        <v>2366</v>
+        <v>2308</v>
       </c>
       <c r="H408" s="4"/>
       <c r="I408" s="4"/>
@@ -20116,7 +20123,7 @@
       <c r="K408" s="4"/>
       <c r="L408" s="4"/>
     </row>
-    <row r="409" spans="1:12" ht="75">
+    <row r="409" spans="1:12" ht="60">
       <c r="A409" s="4">
         <v>409</v>
       </c>
@@ -20136,7 +20143,7 @@
         <v>1851</v>
       </c>
       <c r="G409" s="9" t="s">
-        <v>2392</v>
+        <v>2334</v>
       </c>
       <c r="H409" s="4"/>
       <c r="I409" s="4"/>
@@ -20164,7 +20171,7 @@
         <v>1855</v>
       </c>
       <c r="G410" s="9" t="s">
-        <v>2375</v>
+        <v>2317</v>
       </c>
       <c r="H410" s="4"/>
       <c r="I410" s="4" t="s">
@@ -20196,7 +20203,7 @@
         <v>1859</v>
       </c>
       <c r="G411" s="9" t="s">
-        <v>2394</v>
+        <v>2336</v>
       </c>
       <c r="H411" s="4"/>
       <c r="I411" s="4"/>
@@ -20206,7 +20213,7 @@
       <c r="K411" s="4"/>
       <c r="L411" s="4"/>
     </row>
-    <row r="412" spans="1:12" ht="75">
+    <row r="412" spans="1:12" ht="60">
       <c r="A412" s="4">
         <v>412</v>
       </c>
@@ -20226,7 +20233,7 @@
         <v>1863</v>
       </c>
       <c r="G412" s="9" t="s">
-        <v>2362</v>
+        <v>2304</v>
       </c>
       <c r="H412" s="4"/>
       <c r="I412" s="4"/>
@@ -20256,7 +20263,7 @@
         <v>1867</v>
       </c>
       <c r="G413" s="9" t="s">
-        <v>2344</v>
+        <v>2286</v>
       </c>
       <c r="H413" s="4"/>
       <c r="I413" s="4"/>
@@ -20286,7 +20293,7 @@
         <v>1871</v>
       </c>
       <c r="G414" s="9" t="s">
-        <v>2423</v>
+        <v>2365</v>
       </c>
       <c r="H414" s="4"/>
       <c r="I414" s="4"/>
@@ -20316,7 +20323,7 @@
         <v>1875</v>
       </c>
       <c r="G415" s="9" t="s">
-        <v>2400</v>
+        <v>2342</v>
       </c>
       <c r="H415" s="4"/>
       <c r="I415" s="4"/>
@@ -20346,7 +20353,7 @@
         <v>1879</v>
       </c>
       <c r="G416" s="9" t="s">
-        <v>2419</v>
+        <v>2361</v>
       </c>
       <c r="H416" s="4"/>
       <c r="I416" s="4"/>
@@ -20376,7 +20383,7 @@
         <v>1883</v>
       </c>
       <c r="G417" s="9" t="s">
-        <v>2346</v>
+        <v>2288</v>
       </c>
       <c r="H417" s="4"/>
       <c r="I417" s="4"/>
@@ -20408,7 +20415,7 @@
         <v>1887</v>
       </c>
       <c r="G418" s="9" t="s">
-        <v>2393</v>
+        <v>2335</v>
       </c>
       <c r="H418" s="4"/>
       <c r="I418" s="4" t="s">
@@ -20440,7 +20447,7 @@
         <v>1891</v>
       </c>
       <c r="G419" s="9" t="s">
-        <v>2405</v>
+        <v>2347</v>
       </c>
       <c r="H419" s="4"/>
       <c r="I419" s="4" t="s">
@@ -20452,7 +20459,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="420" spans="1:12" ht="90">
+    <row r="420" spans="1:12" ht="75">
       <c r="A420" s="4">
         <v>420</v>
       </c>
@@ -20472,7 +20479,7 @@
         <v>1895</v>
       </c>
       <c r="G420" s="9" t="s">
-        <v>2404</v>
+        <v>2346</v>
       </c>
       <c r="H420" s="4"/>
       <c r="I420" s="4" t="s">
@@ -20504,7 +20511,7 @@
         <v>1899</v>
       </c>
       <c r="G421" s="9" t="s">
-        <v>2396</v>
+        <v>2338</v>
       </c>
       <c r="H421" s="4"/>
       <c r="I421" s="4"/>
@@ -20532,7 +20539,7 @@
         <v>1903</v>
       </c>
       <c r="G422" s="9" t="s">
-        <v>2365</v>
+        <v>2307</v>
       </c>
       <c r="H422" s="4"/>
       <c r="I422" s="4"/>
@@ -20560,7 +20567,7 @@
         <v>1907</v>
       </c>
       <c r="G423" s="9" t="s">
-        <v>2408</v>
+        <v>2350</v>
       </c>
       <c r="H423" s="4"/>
       <c r="I423" s="4"/>
@@ -20588,7 +20595,7 @@
         <v>1911</v>
       </c>
       <c r="G424" s="9" t="s">
-        <v>2376</v>
+        <v>2318</v>
       </c>
       <c r="H424" s="4"/>
       <c r="I424" s="4"/>
@@ -20618,7 +20625,7 @@
         <v>1915</v>
       </c>
       <c r="G425" s="9" t="s">
-        <v>2402</v>
+        <v>2344</v>
       </c>
       <c r="H425" s="4"/>
       <c r="I425" s="4"/>
@@ -20628,7 +20635,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="426" spans="1:12" ht="60">
+    <row r="426" spans="1:12" ht="45">
       <c r="A426" s="4">
         <v>426</v>
       </c>
@@ -20648,7 +20655,7 @@
         <v>1919</v>
       </c>
       <c r="G426" s="9" t="s">
-        <v>2403</v>
+        <v>2345</v>
       </c>
       <c r="H426" s="4"/>
       <c r="I426" s="4"/>
@@ -20678,7 +20685,7 @@
         <v>1923</v>
       </c>
       <c r="G427" s="9" t="s">
-        <v>2409</v>
+        <v>2351</v>
       </c>
       <c r="H427" s="4"/>
       <c r="I427" s="4"/>
@@ -20706,7 +20713,7 @@
         <v>1927</v>
       </c>
       <c r="G428" s="9" t="s">
-        <v>2410</v>
+        <v>2352</v>
       </c>
       <c r="H428" s="4"/>
       <c r="I428" s="4"/>
@@ -20734,7 +20741,7 @@
         <v>1931</v>
       </c>
       <c r="G429" s="9" t="s">
-        <v>2395</v>
+        <v>2337</v>
       </c>
       <c r="H429" s="4"/>
       <c r="I429" s="4" t="s">
@@ -20764,7 +20771,7 @@
         <v>1935</v>
       </c>
       <c r="G430" s="9" t="s">
-        <v>2431</v>
+        <v>2373</v>
       </c>
       <c r="H430" s="4"/>
       <c r="I430" s="4"/>
@@ -20792,7 +20799,7 @@
         <v>1939</v>
       </c>
       <c r="G431" s="9" t="s">
-        <v>2432</v>
+        <v>2374</v>
       </c>
       <c r="H431" s="4"/>
       <c r="I431" s="4"/>
@@ -20820,7 +20827,7 @@
         <v>1943</v>
       </c>
       <c r="G432" s="9" t="s">
-        <v>2391</v>
+        <v>2333</v>
       </c>
       <c r="H432" s="4"/>
       <c r="I432" s="4" t="s">
@@ -20850,7 +20857,7 @@
         <v>1947</v>
       </c>
       <c r="G433" s="9" t="s">
-        <v>2398</v>
+        <v>2340</v>
       </c>
       <c r="H433" s="4"/>
       <c r="I433" s="4"/>
@@ -20878,7 +20885,7 @@
         <v>1951</v>
       </c>
       <c r="G434" s="9" t="s">
-        <v>2411</v>
+        <v>2353</v>
       </c>
       <c r="H434" s="4"/>
       <c r="I434" s="4"/>
@@ -20910,7 +20917,7 @@
         <v>1955</v>
       </c>
       <c r="G435" s="9" t="s">
-        <v>2360</v>
+        <v>2302</v>
       </c>
       <c r="H435" s="4"/>
       <c r="I435" s="4"/>
@@ -20940,7 +20947,7 @@
         <v>1959</v>
       </c>
       <c r="G436" s="9" t="s">
-        <v>2417</v>
+        <v>2359</v>
       </c>
       <c r="H436" s="4"/>
       <c r="I436" s="4" t="s">
@@ -20970,7 +20977,7 @@
         <v>1963</v>
       </c>
       <c r="G437" s="9" t="s">
-        <v>2429</v>
+        <v>2371</v>
       </c>
       <c r="H437" s="4"/>
       <c r="I437" s="4"/>
@@ -20998,7 +21005,7 @@
         <v>1967</v>
       </c>
       <c r="G438" s="9" t="s">
-        <v>2350</v>
+        <v>2292</v>
       </c>
       <c r="H438" s="4"/>
       <c r="I438" s="4"/>
@@ -21026,7 +21033,7 @@
         <v>1971</v>
       </c>
       <c r="G439" s="9" t="s">
-        <v>2390</v>
+        <v>2332</v>
       </c>
       <c r="H439" s="4"/>
       <c r="I439" s="4"/>
@@ -21036,7 +21043,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="440" spans="1:12" ht="90">
+    <row r="440" spans="1:12" ht="75">
       <c r="A440" s="4">
         <v>440</v>
       </c>
@@ -21056,7 +21063,7 @@
         <v>1975</v>
       </c>
       <c r="G440" s="9" t="s">
-        <v>2345</v>
+        <v>2287</v>
       </c>
       <c r="H440" s="4"/>
       <c r="I440" s="4"/>
@@ -21086,7 +21093,7 @@
         <v>1979</v>
       </c>
       <c r="G441" s="9" t="s">
-        <v>2399</v>
+        <v>2341</v>
       </c>
       <c r="H441" s="4"/>
       <c r="I441" s="4" t="s">
@@ -21118,7 +21125,7 @@
         <v>1983</v>
       </c>
       <c r="G442" s="9" t="s">
-        <v>2426</v>
+        <v>2368</v>
       </c>
       <c r="H442" s="4"/>
       <c r="I442" s="4" t="s">
@@ -21150,7 +21157,7 @@
         <v>1987</v>
       </c>
       <c r="G443" s="9" t="s">
-        <v>2427</v>
+        <v>2369</v>
       </c>
       <c r="H443" s="4"/>
       <c r="I443" s="4" t="s">
@@ -21182,7 +21189,7 @@
         <v>1991</v>
       </c>
       <c r="G444" s="9" t="s">
-        <v>2356</v>
+        <v>2298</v>
       </c>
       <c r="H444" s="4"/>
       <c r="I444" s="4" t="s">
@@ -21214,7 +21221,7 @@
         <v>1995</v>
       </c>
       <c r="G445" s="9" t="s">
-        <v>2424</v>
+        <v>2366</v>
       </c>
       <c r="H445" s="4"/>
       <c r="I445" s="4"/>
@@ -21242,7 +21249,7 @@
         <v>1999</v>
       </c>
       <c r="G446" s="9" t="s">
-        <v>2361</v>
+        <v>2303</v>
       </c>
       <c r="H446" s="4"/>
       <c r="I446" s="4"/>
@@ -21272,7 +21279,7 @@
         <v>2003</v>
       </c>
       <c r="G447" s="9" t="s">
-        <v>2416</v>
+        <v>2358</v>
       </c>
       <c r="H447" s="4"/>
       <c r="I447" s="4"/>
@@ -21356,7 +21363,7 @@
         <v>2012</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>2013</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75">
@@ -21364,19 +21371,19 @@
         <v>1001</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>2014</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>2015</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>2016</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>2017</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75">
@@ -21384,22 +21391,22 @@
         <v>1002</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>94</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>2018</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>2019</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>2020</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>2021</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>2022</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75">
@@ -21407,19 +21414,19 @@
         <v>1003</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>94</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>2023</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>2024</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>2025</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>2026</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75">
@@ -21427,19 +21434,19 @@
         <v>1004</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D6" s="13" t="s">
+        <v>2384</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>2027</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>2028</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>2029</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>2030</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75">
@@ -21447,22 +21454,22 @@
         <v>1005</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>2031</v>
+        <v>2029</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>2030</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>2031</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>2032</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>2033</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>2034</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>2035</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.75">
@@ -21470,19 +21477,19 @@
         <v>1006</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>2036</v>
+        <v>2034</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>2035</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>2036</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>2037</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>2038</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>2039</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75">
@@ -21496,19 +21503,19 @@
         <v>14</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>2038</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>2039</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>2040</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>2041</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>2042</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>2012</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>2013</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15.75">
@@ -21516,19 +21523,19 @@
         <v>1008</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>2043</v>
+        <v>2041</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>94</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>2042</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>2043</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>2044</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>2045</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>2046</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15.75">
@@ -21536,19 +21543,19 @@
         <v>1009</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>2047</v>
+        <v>2045</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>94</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>2046</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>2047</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>2048</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>2049</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>2050</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15.75">
@@ -21556,22 +21563,22 @@
         <v>1010</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>2051</v>
+        <v>2049</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>2050</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>2051</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>2052</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>2053</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>2054</v>
-      </c>
       <c r="G12" s="1" t="s">
-        <v>2030</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15.75">
@@ -21579,22 +21586,22 @@
         <v>1011</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>2055</v>
+        <v>2053</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>2054</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>2055</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>2056</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>2057</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>2058</v>
-      </c>
       <c r="G13" s="1" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15.75">
@@ -21602,22 +21609,22 @@
         <v>1012</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>94</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>2058</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>2059</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>2060</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>2061</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>2062</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>2063</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15.75">
@@ -21625,19 +21632,19 @@
         <v>1013</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>2064</v>
+        <v>2062</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>2065</v>
+        <v>2385</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>2066</v>
+        <v>2063</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>2030</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15.75">
@@ -21645,22 +21652,22 @@
         <v>1014</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>2067</v>
+        <v>2064</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>2068</v>
+        <v>2386</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>2069</v>
+        <v>2065</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>2070</v>
+        <v>2066</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>2050</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15.75">
@@ -21668,22 +21675,22 @@
         <v>1015</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>2071</v>
+        <v>2067</v>
       </c>
       <c r="C17" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>2072</v>
+        <v>2387</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>2073</v>
+        <v>2068</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>2074</v>
+        <v>2069</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>2030</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15.75">
@@ -21691,19 +21698,19 @@
         <v>1016</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>2075</v>
+        <v>2070</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>2076</v>
+        <v>2388</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>2078</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15.75">
@@ -21717,19 +21724,19 @@
         <v>14</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>2079</v>
+        <v>2073</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>2080</v>
+        <v>2074</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>2081</v>
+        <v>2075</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>2030</v>
+        <v>2028</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>2013</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="15.75">
@@ -21737,19 +21744,19 @@
         <v>1018</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>2082</v>
+        <v>2076</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>2083</v>
+        <v>2389</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>2084</v>
+        <v>2077</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>2085</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15.75">
@@ -21757,22 +21764,22 @@
         <v>1019</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>2086</v>
+        <v>2079</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>2087</v>
+        <v>2080</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>2088</v>
+        <v>2081</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>2089</v>
+        <v>2082</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15.75">
@@ -21780,22 +21787,22 @@
         <v>1020</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>2090</v>
+        <v>2083</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>2091</v>
+        <v>2390</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>2092</v>
+        <v>2084</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>2093</v>
+        <v>2085</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>2030</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15.75">
@@ -21803,19 +21810,19 @@
         <v>1021</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>2094</v>
+        <v>2086</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>2095</v>
+        <v>2391</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>2096</v>
+        <v>2087</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>2097</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="15.75">
@@ -21823,19 +21830,19 @@
         <v>1022</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>2098</v>
+        <v>2089</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>2099</v>
+        <v>2392</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>2100</v>
+        <v>2090</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>2085</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15.75">
@@ -21849,19 +21856,19 @@
         <v>14</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>2101</v>
+        <v>2393</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>2102</v>
+        <v>2091</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>2103</v>
+        <v>2092</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>2013</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="15.75">
@@ -21869,22 +21876,22 @@
         <v>1024</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>2104</v>
+        <v>2093</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>2105</v>
+        <v>2394</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>2106</v>
+        <v>2094</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>2107</v>
+        <v>2095</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.75">
@@ -21892,19 +21899,19 @@
         <v>1025</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>2108</v>
+        <v>2096</v>
       </c>
       <c r="C27" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>2109</v>
+        <v>2097</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>2110</v>
+        <v>2098</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>2050</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.75">
@@ -21912,22 +21919,22 @@
         <v>1026</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>2111</v>
+        <v>2099</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>2112</v>
+        <v>2100</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>2113</v>
+        <v>2101</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>2114</v>
+        <v>2102</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>2030</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15.75">
@@ -21935,19 +21942,19 @@
         <v>1027</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>2115</v>
+        <v>2103</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>2116</v>
+        <v>2395</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>2117</v>
+        <v>2104</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>2118</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="15.75">
@@ -21955,19 +21962,19 @@
         <v>1028</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>2119</v>
+        <v>2106</v>
       </c>
       <c r="C30" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>2120</v>
+        <v>2107</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>2121</v>
+        <v>2108</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>2122</v>
+        <v>2109</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>2012</v>
@@ -21978,19 +21985,19 @@
         <v>1029</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>2123</v>
+        <v>2110</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>2124</v>
+        <v>2111</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>2125</v>
+        <v>2112</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>2126</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="15.75">
@@ -21998,22 +22005,22 @@
         <v>1030</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>2127</v>
+        <v>2114</v>
       </c>
       <c r="C32" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>2128</v>
+        <v>2115</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>2129</v>
+        <v>2116</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>2130</v>
+        <v>2117</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -22021,7 +22028,7 @@
         <v>1031</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>2131</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15.75">
@@ -22029,22 +22036,22 @@
         <v>1032</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>2132</v>
+        <v>2119</v>
       </c>
       <c r="C34" s="12" t="s">
         <v>94</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>2133</v>
+        <v>2120</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>2134</v>
+        <v>2121</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>2135</v>
+        <v>2122</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>2136</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15.75">
@@ -22052,19 +22059,19 @@
         <v>1033</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>2137</v>
+        <v>2124</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>94</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>2138</v>
+        <v>2125</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>2139</v>
+        <v>2126</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>2140</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15.75">
@@ -22072,19 +22079,19 @@
         <v>1034</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>2141</v>
+        <v>2128</v>
       </c>
       <c r="C36" s="12" t="s">
         <v>1181</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>2142</v>
+        <v>2129</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>2143</v>
+        <v>2130</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>2144</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15.75">
@@ -22092,19 +22099,19 @@
         <v>1035</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>2145</v>
+        <v>2132</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>1181</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>2146</v>
+        <v>2133</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>2147</v>
+        <v>2134</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>2144</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15.75">
@@ -22112,22 +22119,22 @@
         <v>1036</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>2148</v>
+        <v>2135</v>
       </c>
       <c r="C38" s="12" t="s">
         <v>1181</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>2149</v>
+        <v>2136</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>2150</v>
+        <v>2137</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>2151</v>
+        <v>2138</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>2152</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15.75">
@@ -22135,22 +22142,22 @@
         <v>1037</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>2153</v>
+        <v>2140</v>
       </c>
       <c r="C39" s="12" t="s">
         <v>1181</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>2154</v>
+        <v>2141</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>2155</v>
+        <v>2142</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>2156</v>
+        <v>2143</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>2157</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15.75">
@@ -22158,19 +22165,19 @@
         <v>1038</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>2158</v>
+        <v>2145</v>
       </c>
       <c r="C40" s="12" t="s">
         <v>1181</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>2159</v>
+        <v>2146</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>2160</v>
+        <v>2147</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>2144</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15.75">
@@ -22178,20 +22185,20 @@
         <v>1039</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>2161</v>
+        <v>2148</v>
       </c>
       <c r="C41" s="14" t="s">
         <v>1649</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>2162</v>
+        <v>2149</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>2163</v>
+        <v>2150</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="1" t="s">
-        <v>2164</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15.75">
@@ -22199,20 +22206,20 @@
         <v>1040</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>2165</v>
+        <v>2152</v>
       </c>
       <c r="C42" s="14" t="s">
         <v>1649</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>2166</v>
+        <v>2153</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>2167</v>
+        <v>2154</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="1" t="s">
-        <v>2168</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15.75">
@@ -22220,20 +22227,20 @@
         <v>1041</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>2169</v>
+        <v>2156</v>
       </c>
       <c r="C43" s="14" t="s">
         <v>1649</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>2170</v>
+        <v>2157</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>2171</v>
+        <v>2158</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="1" t="s">
-        <v>2172</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15.75">
@@ -22241,20 +22248,20 @@
         <v>1042</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>2173</v>
+        <v>2160</v>
       </c>
       <c r="C44" s="14" t="s">
         <v>1649</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>2174</v>
+        <v>2161</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>2175</v>
+        <v>2162</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="1" t="s">
-        <v>2176</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15.75">
@@ -22262,20 +22269,20 @@
         <v>1043</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>2177</v>
+        <v>2164</v>
       </c>
       <c r="C45" s="14" t="s">
         <v>1649</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>2178</v>
+        <v>2165</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>2179</v>
+        <v>2166</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="1" t="s">
-        <v>2172</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15.75">
@@ -22283,20 +22290,20 @@
         <v>1044</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>2180</v>
+        <v>2167</v>
       </c>
       <c r="C46" s="14" t="s">
         <v>1649</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>2181</v>
+        <v>2168</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>2182</v>
+        <v>2169</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="1" t="s">
-        <v>2176</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15.75">
@@ -22304,20 +22311,20 @@
         <v>1045</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>2183</v>
+        <v>2170</v>
       </c>
       <c r="C47" s="14" t="s">
         <v>1649</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>2184</v>
+        <v>2171</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>2185</v>
+        <v>2172</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="1" t="s">
-        <v>2186</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15.75">
@@ -22325,20 +22332,20 @@
         <v>1046</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>2187</v>
+        <v>2174</v>
       </c>
       <c r="C48" s="14" t="s">
         <v>1649</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>2188</v>
+        <v>2175</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>2189</v>
+        <v>2176</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="1" t="s">
-        <v>2190</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="15.75">
@@ -22346,20 +22353,20 @@
         <v>1047</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>2191</v>
+        <v>2178</v>
       </c>
       <c r="C49" s="14" t="s">
         <v>1649</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>2192</v>
+        <v>2179</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>2193</v>
+        <v>2180</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="1" t="s">
-        <v>2172</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="15.75">
@@ -22367,20 +22374,20 @@
         <v>1048</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>2194</v>
+        <v>2181</v>
       </c>
       <c r="C50" s="14" t="s">
         <v>1649</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>2195</v>
+        <v>2182</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>2196</v>
+        <v>2183</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="1" t="s">
-        <v>2176</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="15.75">
@@ -22388,20 +22395,20 @@
         <v>1049</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>2197</v>
+        <v>2184</v>
       </c>
       <c r="C51" s="14" t="s">
         <v>1649</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>2198</v>
+        <v>2185</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>2199</v>
+        <v>2186</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="1" t="s">
-        <v>2200</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="15.75">
@@ -22409,22 +22416,22 @@
         <v>1050</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>2201</v>
+        <v>2188</v>
       </c>
       <c r="C52" s="14" t="s">
         <v>1649</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>2202</v>
+        <v>2189</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>2203</v>
+        <v>2190</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>2204</v>
+        <v>2191</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>2205</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="15.75">
@@ -22432,7 +22439,7 @@
         <v>1051</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>2206</v>
+        <v>2193</v>
       </c>
       <c r="C53" s="14" t="s">
         <v>1649</v>
@@ -22476,7 +22483,7 @@
         <v>2006</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>2207</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75">
@@ -22484,7 +22491,7 @@
         <v>2000</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>2208</v>
+        <v>2396</v>
       </c>
       <c r="C2" s="16" t="s">
         <v>14</v>
@@ -22498,7 +22505,7 @@
         <v>2001</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>2209</v>
+        <v>2397</v>
       </c>
       <c r="C3" s="16" t="s">
         <v>14</v>
@@ -22512,7 +22519,7 @@
         <v>2002</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>2210</v>
+        <v>2398</v>
       </c>
       <c r="C4" s="16" t="s">
         <v>14</v>
@@ -22526,7 +22533,7 @@
         <v>2013</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>2211</v>
+        <v>2399</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>14</v>
@@ -22540,7 +22547,7 @@
         <v>2014</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>2212</v>
+        <v>2400</v>
       </c>
       <c r="C6" s="16" t="s">
         <v>14</v>
@@ -22554,7 +22561,7 @@
         <v>2017</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>2213</v>
+        <v>2401</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>14</v>
@@ -22568,7 +22575,7 @@
         <v>2010</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>2214</v>
+        <v>2406</v>
       </c>
       <c r="C8" s="16" t="s">
         <v>14</v>
@@ -22582,7 +22589,7 @@
         <v>2008</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>2215</v>
+        <v>2407</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>14</v>
@@ -22596,7 +22603,7 @@
         <v>2021</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>2216</v>
+        <v>2408</v>
       </c>
       <c r="C10" s="16" t="s">
         <v>14</v>
@@ -22610,7 +22617,7 @@
         <v>2022</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>2217</v>
+        <v>2409</v>
       </c>
       <c r="C11" s="16" t="s">
         <v>14</v>
@@ -22624,7 +22631,7 @@
         <v>2012</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>2218</v>
+        <v>2402</v>
       </c>
       <c r="C12" s="16" t="s">
         <v>14</v>
@@ -22638,7 +22645,7 @@
         <v>2011</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>2219</v>
+        <v>2403</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>14</v>
@@ -22652,7 +22659,7 @@
         <v>2015</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>2220</v>
+        <v>2404</v>
       </c>
       <c r="C14" s="16" t="s">
         <v>14</v>
@@ -22666,7 +22673,7 @@
         <v>2016</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>2221</v>
+        <v>2405</v>
       </c>
       <c r="C15" s="16" t="s">
         <v>14</v>
@@ -22680,7 +22687,7 @@
         <v>2023</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>2222</v>
+        <v>2410</v>
       </c>
       <c r="C16" s="16" t="s">
         <v>14</v>
@@ -22694,7 +22701,7 @@
         <v>2024</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>2223</v>
+        <v>2411</v>
       </c>
       <c r="C17" s="16" t="s">
         <v>14</v>
@@ -22708,19 +22715,19 @@
         <v>2020</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>2224</v>
+        <v>2412</v>
       </c>
       <c r="C18" s="16" t="s">
         <v>94</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>2225</v>
+        <v>2195</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>2226</v>
+        <v>2196</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>2227</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75">
@@ -22728,17 +22735,17 @@
         <v>2003</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>2228</v>
+        <v>2198</v>
       </c>
       <c r="C19" s="16" t="s">
         <v>94</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>2229</v>
+        <v>2199</v>
       </c>
       <c r="E19" s="16"/>
       <c r="F19" s="16" t="s">
-        <v>2230</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75">
@@ -22746,19 +22753,19 @@
         <v>2004</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>2231</v>
+        <v>2413</v>
       </c>
       <c r="C20" s="16" t="s">
         <v>94</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>2232</v>
+        <v>2201</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>2233</v>
+        <v>2202</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>2234</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75">
@@ -22766,17 +22773,17 @@
         <v>2006</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>2235</v>
+        <v>2414</v>
       </c>
       <c r="C21" s="16" t="s">
         <v>94</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>2236</v>
+        <v>2204</v>
       </c>
       <c r="E21" s="16"/>
       <c r="F21" s="16" t="s">
-        <v>2237</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75">
@@ -22784,19 +22791,19 @@
         <v>2005</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>2238</v>
+        <v>2440</v>
       </c>
       <c r="C22" s="16" t="s">
         <v>94</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>2239</v>
+        <v>2206</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>2240</v>
+        <v>2207</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>2241</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75">
@@ -22804,17 +22811,17 @@
         <v>2018</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>2242</v>
+        <v>2415</v>
       </c>
       <c r="C23" s="16" t="s">
         <v>94</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>2243</v>
+        <v>2209</v>
       </c>
       <c r="E23" s="16"/>
       <c r="F23" s="16" t="s">
-        <v>2244</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75">
@@ -22822,19 +22829,19 @@
         <v>2009</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>2245</v>
+        <v>2416</v>
       </c>
       <c r="C24" s="16" t="s">
         <v>94</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>2246</v>
+        <v>2211</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>2247</v>
+        <v>2212</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>2248</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75">
@@ -22842,17 +22849,17 @@
         <v>2025</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>2249</v>
+        <v>2417</v>
       </c>
       <c r="C25" s="16" t="s">
         <v>94</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>2250</v>
+        <v>2214</v>
       </c>
       <c r="E25" s="16"/>
       <c r="F25" s="16" t="s">
-        <v>2251</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75">
@@ -22860,19 +22867,19 @@
         <v>2007</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>2252</v>
+        <v>2418</v>
       </c>
       <c r="C26" s="16" t="s">
         <v>94</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>2253</v>
+        <v>2216</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>2254</v>
+        <v>2217</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>2255</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75">
@@ -22880,17 +22887,17 @@
         <v>2019</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>2256</v>
+        <v>2419</v>
       </c>
       <c r="C27" s="16" t="s">
         <v>94</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>2257</v>
+        <v>2219</v>
       </c>
       <c r="E27" s="11"/>
       <c r="F27" s="16" t="s">
-        <v>2258</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75">
@@ -22898,19 +22905,19 @@
         <v>2031</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>2259</v>
+        <v>2420</v>
       </c>
       <c r="C28" s="16" t="s">
         <v>1181</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>2260</v>
+        <v>2221</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>2261</v>
+        <v>2222</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>2262</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75">
@@ -22918,19 +22925,19 @@
         <v>2030</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>2263</v>
+        <v>2421</v>
       </c>
       <c r="C29" s="16" t="s">
         <v>1181</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>2264</v>
+        <v>2224</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>2265</v>
+        <v>2225</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>2262</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75">
@@ -22938,19 +22945,19 @@
         <v>2033</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>2266</v>
+        <v>2422</v>
       </c>
       <c r="C30" s="16" t="s">
         <v>1181</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>2267</v>
+        <v>2226</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>2268</v>
+        <v>2227</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>2262</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75">
@@ -22958,19 +22965,19 @@
         <v>2032</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>2269</v>
+        <v>2423</v>
       </c>
       <c r="C31" s="16" t="s">
         <v>1181</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>2270</v>
+        <v>2228</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>2270</v>
+        <v>2228</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>2271</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75">
@@ -22978,19 +22985,19 @@
         <v>2026</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>2272</v>
+        <v>2424</v>
       </c>
       <c r="C32" s="16" t="s">
         <v>1181</v>
       </c>
       <c r="D32" s="18" t="s">
-        <v>2273</v>
+        <v>2230</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>2274</v>
+        <v>2231</v>
       </c>
       <c r="F32" s="16" t="s">
-        <v>2275</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.75">
@@ -22998,19 +23005,19 @@
         <v>2027</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>2276</v>
+        <v>2425</v>
       </c>
       <c r="C33" s="16" t="s">
         <v>1181</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>2277</v>
+        <v>2233</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>2278</v>
+        <v>2234</v>
       </c>
       <c r="F33" s="16" t="s">
-        <v>2275</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15.75">
@@ -23018,19 +23025,19 @@
         <v>2029</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>2279</v>
+        <v>2426</v>
       </c>
       <c r="C34" s="16" t="s">
         <v>1181</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>2280</v>
+        <v>2235</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>2281</v>
+        <v>2236</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>2282</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75">
@@ -23038,14 +23045,14 @@
         <v>2028</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>2283</v>
+        <v>2439</v>
       </c>
       <c r="C35" s="16" t="s">
         <v>1181</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="16" t="s">
-        <v>2284</v>
+        <v>2238</v>
       </c>
       <c r="F35" s="16"/>
     </row>
@@ -23053,18 +23060,18 @@
       <c r="A36" s="11">
         <v>2043</v>
       </c>
-      <c r="B36" s="16" t="s">
-        <v>2285</v>
+      <c r="B36" s="26" t="s">
+        <v>2427</v>
       </c>
       <c r="C36" s="16" t="s">
         <v>1649</v>
       </c>
       <c r="D36" s="19" t="s">
-        <v>2286</v>
+        <v>2239</v>
       </c>
       <c r="E36" s="16"/>
       <c r="F36" s="16" t="s">
-        <v>2287</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15.75">
@@ -23072,19 +23079,19 @@
         <v>2040</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>2288</v>
+        <v>2428</v>
       </c>
       <c r="C37" s="16" t="s">
         <v>1649</v>
       </c>
       <c r="D37" s="19" t="s">
-        <v>2289</v>
+        <v>2241</v>
       </c>
       <c r="E37" s="20" t="s">
-        <v>2290</v>
+        <v>2242</v>
       </c>
       <c r="F37" s="16" t="s">
-        <v>2291</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15.75">
@@ -23092,19 +23099,19 @@
         <v>2035</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>2292</v>
+        <v>2429</v>
       </c>
       <c r="C38" s="16" t="s">
         <v>1649</v>
       </c>
       <c r="D38" s="19" t="s">
-        <v>2293</v>
+        <v>2244</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>2294</v>
+        <v>2245</v>
       </c>
       <c r="F38" s="16" t="s">
-        <v>2295</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15.75">
@@ -23112,19 +23119,19 @@
         <v>2041</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>2296</v>
+        <v>2433</v>
       </c>
       <c r="C39" s="16" t="s">
         <v>1649</v>
       </c>
       <c r="D39" s="19" t="s">
-        <v>2297</v>
+        <v>2247</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>2298</v>
+        <v>2248</v>
       </c>
       <c r="F39" s="16" t="s">
-        <v>2299</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15.75">
@@ -23132,19 +23139,19 @@
         <v>2042</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>2300</v>
+        <v>2434</v>
       </c>
       <c r="C40" s="16" t="s">
         <v>1649</v>
       </c>
       <c r="D40" s="19" t="s">
-        <v>2301</v>
+        <v>2250</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>2302</v>
+        <v>2251</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>2299</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.75">
@@ -23152,19 +23159,19 @@
         <v>2044</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>2303</v>
+        <v>2430</v>
       </c>
       <c r="C41" s="16" t="s">
         <v>1649</v>
       </c>
       <c r="D41" s="19" t="s">
-        <v>2304</v>
+        <v>2252</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>2305</v>
+        <v>2253</v>
       </c>
       <c r="F41" s="16" t="s">
-        <v>2306</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="15.75">
@@ -23172,17 +23179,17 @@
         <v>2036</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>2307</v>
+        <v>2431</v>
       </c>
       <c r="C42" s="16" t="s">
         <v>1649</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>2308</v>
+        <v>2255</v>
       </c>
       <c r="E42" s="16"/>
       <c r="F42" s="16" t="s">
-        <v>2309</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="15.75">
@@ -23190,19 +23197,19 @@
         <v>2034</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>2310</v>
+        <v>2432</v>
       </c>
       <c r="C43" s="16" t="s">
         <v>1649</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>2311</v>
+        <v>2257</v>
       </c>
       <c r="E43" s="16" t="s">
-        <v>2312</v>
+        <v>2258</v>
       </c>
       <c r="F43" s="16" t="s">
-        <v>2313</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="15.75">
@@ -23210,19 +23217,19 @@
         <v>2037</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>2314</v>
+        <v>2436</v>
       </c>
       <c r="C44" s="16" t="s">
         <v>1649</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>2315</v>
+        <v>2260</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>2316</v>
+        <v>2261</v>
       </c>
       <c r="F44" s="16" t="s">
-        <v>2317</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15.75">
@@ -23230,19 +23237,19 @@
         <v>2038</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>2318</v>
+        <v>2437</v>
       </c>
       <c r="C45" s="16" t="s">
         <v>1649</v>
       </c>
       <c r="D45" s="19" t="s">
-        <v>2319</v>
+        <v>2263</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>2320</v>
+        <v>2264</v>
       </c>
       <c r="F45" s="16" t="s">
-        <v>2317</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="15.75">
@@ -23250,19 +23257,19 @@
         <v>2039</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>2321</v>
+        <v>2438</v>
       </c>
       <c r="C46" s="16" t="s">
         <v>1649</v>
       </c>
       <c r="D46" s="19" t="s">
-        <v>2322</v>
+        <v>2265</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>2323</v>
+        <v>2266</v>
       </c>
       <c r="F46" s="16" t="s">
-        <v>2317</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.75">
@@ -23270,19 +23277,19 @@
         <v>2045</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>2324</v>
+        <v>2435</v>
       </c>
       <c r="C47" s="16" t="s">
         <v>1649</v>
       </c>
       <c r="D47" s="19" t="s">
-        <v>2325</v>
+        <v>2267</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>2326</v>
+        <v>2268</v>
       </c>
       <c r="F47" s="16" t="s">
-        <v>2327</v>
+        <v>2269</v>
       </c>
     </row>
   </sheetData>
@@ -23311,55 +23318,55 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2328</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>2329</v>
+        <v>2271</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>2330</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="13.5" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>2331</v>
+        <v>2273</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>2332</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="13.5" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>2333</v>
+        <v>2275</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>2334</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>2335</v>
+        <v>2277</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>2336</v>
+        <v>2278</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>2337</v>
+        <v>2279</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>2338</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>2339</v>
+        <v>2281</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>2340</v>
+        <v>2282</v>
       </c>
     </row>
   </sheetData>
@@ -23385,12 +23392,12 @@
         <v>2005</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>2341</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="12.75" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>2342</v>
+        <v>2284</v>
       </c>
       <c r="B2" s="23" t="b">
         <f>FALSE()</f>
